--- a/SGC-CKN/Excel/1ee6f1eb-da1d-4cd9-a028-95ffefa3bfb6_Cọc_khoan_nhồi_P1-61_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/1ee6f1eb-da1d-4cd9-a028-95ffefa3bfb6_Cọc_khoan_nhồi_P1-61_D800_31-03-2026.xlsx
@@ -1324,16 +1324,16 @@
         <v>-21.56</v>
       </c>
       <c r="G16" s="22">
-        <v>-28.56</v>
+        <v>-25.56</v>
       </c>
       <c r="H16" s="22">
         <v>2.17</v>
       </c>
       <c r="I16" s="22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J16" s="8">
-        <v>3.23</v>
+        <v>1.85</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>29</v>
@@ -1356,7 +1356,7 @@
         <v>48</v>
       </c>
       <c r="F17" s="25">
-        <v>-28.56</v>
+        <v>-25.56</v>
       </c>
       <c r="G17" s="25">
         <v>-38.5</v>
@@ -1365,10 +1365,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" s="25">
-        <v>9.94</v>
+        <v>12.94</v>
       </c>
       <c r="J17" s="12">
-        <v>8.4</v>
+        <v>10.94</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>29</v>
@@ -1706,16 +1706,16 @@
         <v>-21.56</v>
       </c>
       <c r="F7" s="22">
-        <v>-28.56</v>
+        <v>-25.56</v>
       </c>
       <c r="G7" s="22">
         <v>2.17</v>
       </c>
       <c r="H7" s="22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I7" s="8">
-        <v>3.23</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1732,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-28.56</v>
+        <v>-25.56</v>
       </c>
       <c r="F8" s="25">
         <v>-38.5</v>
@@ -1741,10 +1741,10 @@
         <v>1.18</v>
       </c>
       <c r="H8" s="25">
-        <v>9.94</v>
+        <v>12.94</v>
       </c>
       <c r="I8" s="12">
-        <v>8.4</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
